--- a/Nissan_failed_to_download.xlsx
+++ b/Nissan_failed_to_download.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renana\PycharmProjects\AdExtracterBot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nir\PycharmProjects\AdExtracterBot\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64765E7D-612E-4695-AA9E-805D0BF9B949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13230"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,9 +21,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
-  <si>
-    <t>Values</t>
-  </si>
   <si>
     <t>3410316173</t>
   </si>
@@ -158,16 +156,19 @@
   <si>
     <t>15282646783</t>
   </si>
+  <si>
+    <t>MASTER CREATIVE ID</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -518,238 +519,238 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1966"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:A2094"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
@@ -10350,6 +10351,646 @@
     <row r="1966" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1966">
         <v>587351902</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1967">
+        <v>15283198742</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1968">
+        <v>15262813278</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1969">
+        <v>15263172191</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1970">
+        <v>15264355448</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1971">
+        <v>15265653102</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1972">
+        <v>15267302201</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1973">
+        <v>15269622878</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1974">
+        <v>15285309622</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1975">
+        <v>15262153722</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1976">
+        <v>15262990690</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1977">
+        <v>15262999267</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1978">
+        <v>15269393135</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1979">
+        <v>15277052283</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1980">
+        <v>15278608354</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1981">
+        <v>15280239633</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1982">
+        <v>15283286887</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1983">
+        <v>15284125244</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1984">
+        <v>15284731390</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1985">
+        <v>15284899591</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1986">
+        <v>15269394905</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1987">
+        <v>15269790400</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1988">
+        <v>15281781789</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1989">
+        <v>15285302786</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1990">
+        <v>15271180260</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1991">
+        <v>15271679763</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1992">
+        <v>15267044793</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1993">
+        <v>15267783798</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1994">
+        <v>15269400264</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1995">
+        <v>15273895474</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1996">
+        <v>15267044794</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1997">
+        <v>15267078890</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1998">
+        <v>15267797565</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1999">
+        <v>15265004649</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2000">
+        <v>15279081576</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2001">
+        <v>15280048796</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2002">
+        <v>15282155337</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2003">
+        <v>15280233412</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2004">
+        <v>15280626686</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2005">
+        <v>15286031949</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2006">
+        <v>15266547044</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2007">
+        <v>15266613907</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2008">
+        <v>15267873625</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2009">
+        <v>15280236218</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2010">
+        <v>15276779140</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2011">
+        <v>15280233301</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2012">
+        <v>15280233418</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2013">
+        <v>15281682659</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2014">
+        <v>15282158506</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2015">
+        <v>15270663495</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2016">
+        <v>15267580091</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2017">
+        <v>15283798423</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2018">
+        <v>15271131424</v>
+      </c>
+    </row>
+    <row r="2019" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2019">
+        <v>15278452487</v>
+      </c>
+    </row>
+    <row r="2020" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2020">
+        <v>15266090465</v>
+      </c>
+    </row>
+    <row r="2021" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2021">
+        <v>15266432495</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2022">
+        <v>15266585154</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2023">
+        <v>15267460338</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2024">
+        <v>15268930143</v>
+      </c>
+    </row>
+    <row r="2025" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2025">
+        <v>15274130737</v>
+      </c>
+    </row>
+    <row r="2026" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2026">
+        <v>15277937109</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2027">
+        <v>15278415731</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2028">
+        <v>15280233195</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2029">
+        <v>15280233377</v>
+      </c>
+    </row>
+    <row r="2030" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2030">
+        <v>15280235412</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2031">
+        <v>15280275909</v>
+      </c>
+    </row>
+    <row r="2032" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2032">
+        <v>15283859421</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2033">
+        <v>15284207786</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2034">
+        <v>3541264081</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2035">
+        <v>15269980290</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2036">
+        <v>15278413311</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2037">
+        <v>15278418630</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2038">
+        <v>15280236038</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2039">
+        <v>15280236916</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2040">
+        <v>15281383613</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2041">
+        <v>15281922377</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2042">
+        <v>15282625344</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2043">
+        <v>15283518163</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2044">
+        <v>15283518204</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2045">
+        <v>15283521257</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2046">
+        <v>15283525813</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2047">
+        <v>15278479793</v>
+      </c>
+    </row>
+    <row r="2048" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2048">
+        <v>15284731932</v>
+      </c>
+    </row>
+    <row r="2049" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2049">
+        <v>15267196770</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2050">
+        <v>15267207920</v>
+      </c>
+    </row>
+    <row r="2051" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2051">
+        <v>15267237139</v>
+      </c>
+    </row>
+    <row r="2052" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2052">
+        <v>15267329849</v>
+      </c>
+    </row>
+    <row r="2053" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2053">
+        <v>15280137079</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2054">
+        <v>15280236066</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2055">
+        <v>15282419825</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2056">
+        <v>15283124269</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2057">
+        <v>15283515118</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2058">
+        <v>15283517688</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2059">
+        <v>15283574476</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2060">
+        <v>15284773972</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2061">
+        <v>15284932316</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2062">
+        <v>15285724490</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2063">
+        <v>15265433997</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2064">
+        <v>15266536807</v>
+      </c>
+    </row>
+    <row r="2065" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2065">
+        <v>15266577207</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2066">
+        <v>15267283887</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2067">
+        <v>15278439774</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2068">
+        <v>15284936053</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2069">
+        <v>15265230261</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2070">
+        <v>15265240741</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2071">
+        <v>15265656442</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2072">
+        <v>15267196628</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2073">
+        <v>15267196660</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2074">
+        <v>15280341270</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2075">
+        <v>15282276836</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2076">
+        <v>15285385687</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2077">
+        <v>15285578609</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2078">
+        <v>15265855761</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2079">
+        <v>15280373158</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2080">
+        <v>15281255630</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2081">
+        <v>15284931965</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2082">
+        <v>15285378104</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2083">
+        <v>15265252187</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2084">
+        <v>15267215641</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2085">
+        <v>15267365406</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2086">
+        <v>15277967272</v>
+      </c>
+    </row>
+    <row r="2087" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2087">
+        <v>15283580832</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2088">
+        <v>15283793427</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2089">
+        <v>15284269618</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2090">
+        <v>15276533808</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2091">
+        <v>15266620464</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2092">
+        <v>15268466216</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2093">
+        <v>15268697726</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2094">
+        <v>15277325778</v>
       </c>
     </row>
   </sheetData>
